--- a/초과지출사업.xlsx
+++ b/초과지출사업.xlsx
@@ -384,406 +384,406 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2019010100065</t>
+          <t>2023070100417</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>사단법인 메디피스</t>
         </is>
       </c>
       <c r="C2">
-        <v>1.938195</v>
+        <v>127.1945196211096</v>
       </c>
       <c r="D2">
-        <v>775278</v>
+        <v>375987</v>
       </c>
       <c r="E2">
-        <v>400000</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023070100488</t>
+          <t>2023070100509</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>사단법인 라파엘인터내셔널</t>
+          <t>어린이재단</t>
         </is>
       </c>
       <c r="C3">
-        <v>9.795104214677114</v>
+        <v>78.06304585152839</v>
       </c>
       <c r="D3">
-        <v>191269</v>
+        <v>286023</v>
       </c>
       <c r="E3">
-        <v>19527</v>
+        <v>3664</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023070100521</t>
+          <t>2023070100403</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>사회복지법인 밀알복지재단, 향기내는사람들</t>
+          <t>사회복지법인 월드비전</t>
         </is>
       </c>
       <c r="C4">
-        <v>15.35460024641204</v>
+        <v>51.80785532636338</v>
       </c>
       <c r="D4">
-        <v>461114</v>
+        <v>366696</v>
       </c>
       <c r="E4">
-        <v>30031</v>
+        <v>7078</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023070100520</t>
+          <t>2022070100399</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>사회복지법인 밀알복지재단</t>
+          <t>초록우산 어린이재단</t>
         </is>
       </c>
       <c r="C5">
-        <v>5.88633360510557</v>
+        <v>37.9321708290232</v>
       </c>
       <c r="D5">
-        <v>209371</v>
+        <v>256687</v>
       </c>
       <c r="E5">
-        <v>35569</v>
+        <v>6767</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023070100536</t>
+          <t>2023070100438</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>사단법인 열매나눔인터내셔널</t>
+          <t>한국해비타트</t>
         </is>
       </c>
       <c r="C6">
-        <v>4.344073671472814</v>
+        <v>24.19796753332453</v>
       </c>
       <c r="D6">
-        <v>211804</v>
+        <v>366696</v>
       </c>
       <c r="E6">
-        <v>48757</v>
+        <v>15154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023070100417</t>
+          <t>2019010100062</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>사단법인 메디피스</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="C7">
-        <v>127.1945196211096</v>
+        <v>16.8901</v>
       </c>
       <c r="D7">
-        <v>375987</v>
+        <v>337802</v>
       </c>
       <c r="E7">
-        <v>2956</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023070100522</t>
+          <t>2021070101657</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>굿파머스</t>
+          <t>지구촌나눔운동</t>
         </is>
       </c>
       <c r="C8">
-        <v>7.111599833834275</v>
+        <v>16.87821043910522</v>
       </c>
       <c r="D8">
-        <v>291028</v>
+        <v>733392</v>
       </c>
       <c r="E8">
-        <v>40923</v>
+        <v>43452</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2020010100020</t>
+          <t>2023070100521</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>사회복지법인 밀알복지재단, 향기내는사람들</t>
         </is>
       </c>
       <c r="C9">
-        <v>5.369857718478166</v>
+        <v>15.35460024641204</v>
       </c>
       <c r="D9">
-        <v>2097649</v>
+        <v>461114</v>
       </c>
       <c r="E9">
-        <v>390634</v>
+        <v>30031</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2021010100097</t>
+          <t>2023070100550</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>사단법인 비전케어</t>
         </is>
       </c>
       <c r="C10">
-        <v>1.443339024390244</v>
+        <v>10.51251128066289</v>
       </c>
       <c r="D10">
-        <v>591769</v>
+        <v>256274</v>
       </c>
       <c r="E10">
-        <v>410000</v>
+        <v>24378</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023070100509</t>
+          <t>2023070100534</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>어린이재단</t>
+          <t>(사)한국국제기아대책기구</t>
         </is>
       </c>
       <c r="C11">
-        <v>78.06304585152839</v>
+        <v>10.04925944416708</v>
       </c>
       <c r="D11">
-        <v>286023</v>
+        <v>301930</v>
       </c>
       <c r="E11">
-        <v>3664</v>
+        <v>30045</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023070100453</t>
+          <t>2023070100488</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>사단법인 캠프</t>
+          <t>사단법인 라파엘인터내셔널</t>
         </is>
       </c>
       <c r="C12">
-        <v>5.534886641964454</v>
+        <v>9.795104214677114</v>
       </c>
       <c r="D12">
-        <v>264396</v>
+        <v>191269</v>
       </c>
       <c r="E12">
-        <v>47769</v>
+        <v>19527</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023070100533</t>
+          <t>2023070100461</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>사)아시아위민브릿지 두런두런</t>
+          <t>월드투게더</t>
         </is>
       </c>
       <c r="C13">
-        <v>5.285096181956382</v>
+        <v>9.284980480788986</v>
       </c>
       <c r="D13">
-        <v>90391</v>
+        <v>90380</v>
       </c>
       <c r="E13">
-        <v>17103</v>
+        <v>9734</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2020010100063</t>
+          <t>2023070100517</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>굿네이버스인터내셔날,한국건강관리협회</t>
         </is>
       </c>
       <c r="C14">
-        <v>3.765487368421053</v>
+        <v>8.530803413097448</v>
       </c>
       <c r="D14">
-        <v>3577213</v>
+        <v>408907</v>
       </c>
       <c r="E14">
-        <v>950000</v>
+        <v>47933</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023070100403</t>
+          <t>2023070100405</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>사회복지법인 월드비전</t>
+          <t>재단법인 굿네이버스 글로벌 임팩트</t>
         </is>
       </c>
       <c r="C15">
-        <v>51.80785532636338</v>
+        <v>7.736017794491962</v>
       </c>
       <c r="D15">
-        <v>366696</v>
+        <v>337360</v>
       </c>
       <c r="E15">
-        <v>7078</v>
+        <v>43609</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023010100037</t>
+          <t>2023070100427</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>사단법인 더멋진세상</t>
         </is>
       </c>
       <c r="C16">
-        <v>1.541298823529412</v>
+        <v>7.123928139672186</v>
       </c>
       <c r="D16">
-        <v>1310104</v>
+        <v>253391</v>
       </c>
       <c r="E16">
-        <v>850000</v>
+        <v>35569</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023010103543</t>
+          <t>2023070100522</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>굿파머스</t>
         </is>
       </c>
       <c r="C17">
-        <v>4.22046</v>
+        <v>7.111599833834275</v>
       </c>
       <c r="D17">
-        <v>422046</v>
+        <v>291028</v>
       </c>
       <c r="E17">
-        <v>100000</v>
+        <v>40923</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023070100511</t>
+          <t>2023070100512</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>사단법인 열매나눔인터네셔널</t>
+          <t>(사)한국국제기아대책기구</t>
         </is>
       </c>
       <c r="C18">
-        <v>4.412396446377029</v>
+        <v>6.986081437727787</v>
       </c>
       <c r="D18">
-        <v>235419</v>
+        <v>222353</v>
       </c>
       <c r="E18">
-        <v>53354</v>
+        <v>31828</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023070100534</t>
+          <t>2023070100520</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>(사)한국국제기아대책기구</t>
+          <t>사회복지법인 밀알복지재단</t>
         </is>
       </c>
       <c r="C19">
-        <v>10.04925944416708</v>
+        <v>5.88633360510557</v>
       </c>
       <c r="D19">
-        <v>301930</v>
+        <v>209371</v>
       </c>
       <c r="E19">
-        <v>30045</v>
+        <v>35569</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023070100512</t>
+          <t>2023070100453</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>(사)한국국제기아대책기구</t>
+          <t>사단법인 캠프</t>
         </is>
       </c>
       <c r="C20">
-        <v>6.986081437727787</v>
+        <v>5.534886641964454</v>
       </c>
       <c r="D20">
-        <v>222353</v>
+        <v>264396</v>
       </c>
       <c r="E20">
-        <v>31828</v>
+        <v>47769</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2021010100100</t>
+          <t>2020010100020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -792,139 +792,139 @@
         </is>
       </c>
       <c r="C21">
-        <v>2.101392929292929</v>
+        <v>5.369857718478166</v>
       </c>
       <c r="D21">
-        <v>2080379</v>
+        <v>2097649</v>
       </c>
       <c r="E21">
-        <v>990000</v>
+        <v>390634</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2019010100062</t>
+          <t>2023070100533</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>사)아시아위민브릿지 두런두런</t>
         </is>
       </c>
       <c r="C22">
-        <v>16.8901</v>
+        <v>5.285096181956382</v>
       </c>
       <c r="D22">
-        <v>337802</v>
+        <v>90391</v>
       </c>
       <c r="E22">
-        <v>20000</v>
+        <v>17103</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023070100438</t>
+          <t>2023070100511</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한국해비타트</t>
+          <t>사단법인 열매나눔인터네셔널</t>
         </is>
       </c>
       <c r="C23">
-        <v>24.19796753332453</v>
+        <v>4.412396446377029</v>
       </c>
       <c r="D23">
-        <v>366696</v>
+        <v>235419</v>
       </c>
       <c r="E23">
-        <v>15154</v>
+        <v>53354</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023070100517</t>
+          <t>2023070100404</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>굿네이버스인터내셔날,한국건강관리협회</t>
+          <t>사단법인 글로벌케어</t>
         </is>
       </c>
       <c r="C24">
-        <v>8.530803413097448</v>
+        <v>4.38221485000984</v>
       </c>
       <c r="D24">
-        <v>408907</v>
+        <v>155871</v>
       </c>
       <c r="E24">
-        <v>47933</v>
+        <v>35569</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2023070100405</t>
+          <t>2023070100536</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>재단법인 굿네이버스 글로벌 임팩트</t>
+          <t>사단법인 열매나눔인터내셔널</t>
         </is>
       </c>
       <c r="C25">
-        <v>7.736017794491962</v>
+        <v>4.344073671472814</v>
       </c>
       <c r="D25">
-        <v>337360</v>
+        <v>211804</v>
       </c>
       <c r="E25">
-        <v>43609</v>
+        <v>48757</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2023070100404</t>
+          <t>2023010103543</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>사단법인 글로벌케어</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="C26">
-        <v>4.38221485000984</v>
+        <v>4.22046</v>
       </c>
       <c r="D26">
-        <v>155871</v>
+        <v>422046</v>
       </c>
       <c r="E26">
-        <v>35569</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2021070101657</t>
+          <t>2020010100063</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>지구촌나눔운동</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="C27">
-        <v>16.87821043910522</v>
+        <v>3.765487368421053</v>
       </c>
       <c r="D27">
-        <v>733392</v>
+        <v>3577213</v>
       </c>
       <c r="E27">
-        <v>43452</v>
+        <v>950000</v>
       </c>
     </row>
     <row r="28">
@@ -951,85 +951,85 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2022070100399</t>
+          <t>2021010100100</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>초록우산 어린이재단</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="C29">
-        <v>37.9321708290232</v>
+        <v>2.101392929292929</v>
       </c>
       <c r="D29">
-        <v>256687</v>
+        <v>2080379</v>
       </c>
       <c r="E29">
-        <v>6767</v>
+        <v>990000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2023070100427</t>
+          <t>2019010100065</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>사단법인 더멋진세상</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="C30">
-        <v>7.123928139672186</v>
+        <v>1.938195</v>
       </c>
       <c r="D30">
-        <v>253391</v>
+        <v>775278</v>
       </c>
       <c r="E30">
-        <v>35569</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2023070100461</t>
+          <t>2023010100037</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>월드투게더</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="C31">
-        <v>9.284980480788986</v>
+        <v>1.541298823529412</v>
       </c>
       <c r="D31">
-        <v>90380</v>
+        <v>1310104</v>
       </c>
       <c r="E31">
-        <v>9734</v>
+        <v>850000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2023070100550</t>
+          <t>2021010100097</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>사단법인 비전케어</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="C32">
-        <v>10.51251128066289</v>
+        <v>1.443339024390244</v>
       </c>
       <c r="D32">
-        <v>256274</v>
+        <v>591769</v>
       </c>
       <c r="E32">
-        <v>24378</v>
+        <v>410000</v>
       </c>
     </row>
   </sheetData>
